--- a/nba_picks_tracker.xlsx
+++ b/nba_picks_tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="All Picks" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Pending Picks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Performance" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Profit Tracker" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Picks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit Tracker" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -55,14 +55,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -90,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -104,11 +104,14 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -475,12 +478,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N68"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
@@ -568,595 +571,587 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>OG Anunoby</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>OG Anunoby</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Nickeil Alexander-Walker</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>OG Anunoby</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Austin Reaves</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G7" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H7" s="3" t="n">
         <v>-35.2</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>DAL</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="N2" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>67</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="N7" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Caleb Martin</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Cam Thomas</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>PRA</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>LAL</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="F8" s="4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Lauri Markkanen</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>PRA</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Aaron Wiggins</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>-37.7</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Chet Holmgren</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="F10" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Cam Thomas</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>PRA</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Kevin Porter Jr.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>-78.3</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>OKC</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Myles Turner</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>OKC</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Aaron Wiggins</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>-37.7</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Chet Holmgren</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Kevin Porter Jr.</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>-78.3</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>OKC</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
+      <c r="M11" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="N9" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>De'Aaron Fox</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>GSW</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Victor Wembanyama</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>148.8</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>GSW</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N11" s="2" t="n">
+      <c r="N11" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -1165,7 +1160,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1179,22 +1174,22 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>22.5</v>
+        <v>18.5</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>33</v>
+        <v>24.5</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>46.6</v>
+        <v>32.4</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -1204,75 +1199,79 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr"/>
-      <c r="N12" s="3" t="n"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Dillon Brooks</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>-33.7</v>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>OKC</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v>0</v>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Victor Wembanyama</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
@@ -1281,31 +1280,31 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.5</v>
+        <v>19.5</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.6</v>
+        <v>12.9</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>83.09999999999999</v>
+        <v>-33.7</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1324,7 +1323,7 @@
         </is>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="N14" s="4" t="n">
         <v>0</v>
@@ -1332,7 +1331,7 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
@@ -1341,12 +1340,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1355,17 +1354,17 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>59</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1392,7 +1391,7 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
@@ -1401,36 +1400,36 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Jaime Jaquez Jr.</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>15.5</v>
+        <v>3.5</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-49.6</v>
+        <v>59</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -1444,195 +1443,195 @@
         </is>
       </c>
       <c r="M16" s="4" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Jaime Jaquez Jr.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>-49.6</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Trey Murphy III</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F18" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="G18" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="H18" s="3" t="n">
         <v>-33</v>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M17" s="2" t="n">
+      <c r="M18" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="N17" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="N18" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Tyrese Maxey</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>REB</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F19" s="4" t="n">
         <v>3.5</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>6.7</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>NYK</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="M18" s="4" t="n">
+      <c r="M19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="N18" s="4" t="n">
+      <c r="N19" s="4" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Kelly Oubre Jr.</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>REB</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>NYK</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -1641,12 +1640,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1655,22 +1654,22 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>21</v>
+        <v>6.3</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>35.2</v>
+        <v>40.9</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -1680,431 +1679,431 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="3" t="n"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>OG Anunoby</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Karl-Anthony Towns</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F22" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="G22" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="H22" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M21" s="2" t="n">
+      <c r="M22" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="N21" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Collin Sexton</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>-41.9</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" s="2" t="n">
+      <c r="N22" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Collin Sexton</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>-41.9</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Andrew Nembhard</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="F24" s="2" t="n">
         <v>18.5</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="G24" s="2" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="H24" s="2" t="n">
         <v>-50.1</v>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>BKN</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Brandon Ingram</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F25" s="4" t="n">
         <v>3.5</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>4.7</v>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>35.7</v>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="M24" s="4" t="n">
+      <c r="M25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="4" t="n">
+      <c r="N25" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
+    <row r="26">
+      <c r="A26" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Ausar Thompson</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F26" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G26" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="H26" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M25" s="2" t="n">
+      <c r="M26" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="N25" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="N26" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Dyson Daniels</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="F27" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="G27" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="H27" s="3" t="n">
         <v>40.7</v>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>CHA</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M26" s="2" t="n">
+      <c r="M27" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="N26" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>LaMelo Ball</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>REB</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N27" s="4" t="n">
-        <v>0</v>
+      <c r="N27" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
@@ -2113,36 +2112,36 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.2</v>
+        <v>7.9</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-50.1</v>
+        <v>44.4</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -2156,431 +2155,431 @@
         </is>
       </c>
       <c r="M28" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Jalen Johnson</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>-50.1</v>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Paolo Banchero</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>REB</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="F30" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="G30" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="H30" s="3" t="n">
         <v>-39.7</v>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M29" s="2" t="n">
+      <c r="M30" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="N29" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
+      <c r="N30" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Jalen Suggs</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>REB</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F31" s="4" t="n">
         <v>4.5</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>6.5</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>44.2</v>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="M30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" s="4" t="n">
+      <c r="M31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
+    <row r="32">
+      <c r="A32" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>Myles Turner</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="F32" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G32" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="H31" s="2" t="n">
+      <c r="H32" s="3" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>ORL</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M31" s="2" t="n">
+      <c r="M32" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N31" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="N32" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Desmond Bane</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="F33" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G33" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="H33" s="3" t="n">
         <v>72.3</v>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M32" s="2" t="n">
+      <c r="M33" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="N32" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Julian Champagnie</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>-35.4</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>LAL</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N33" s="2" t="n">
+      <c r="N33" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Julian Champagnie</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>-35.4</v>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>LeBron James</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>REB</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F34" s="3" t="n">
+      <c r="F35" s="2" t="n">
         <v>5.5</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G35" s="2" t="n">
         <v>7.2</v>
       </c>
-      <c r="H34" s="3" t="n">
+      <c r="H35" s="2" t="n">
         <v>31.6</v>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>SAS</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr"/>
-      <c r="N34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>De'Aaron Fox</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>LAL</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="N35" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
@@ -2589,12 +2588,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -2603,13 +2602,13 @@
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>2.5</v>
+        <v>17.5</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>6</v>
+        <v>24.9</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>138.8</v>
+        <v>42.4</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
@@ -2632,131 +2631,131 @@
         </is>
       </c>
       <c r="M36" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N36" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Victor Wembanyama</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>138.8</v>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Klay Thompson</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F37" s="3" t="n">
+      <c r="F38" s="2" t="n">
         <v>8.5</v>
       </c>
-      <c r="G37" s="3" t="n">
+      <c r="G38" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="H37" s="3" t="n">
+      <c r="H38" s="2" t="n">
         <v>29.9</v>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>PHX</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>Cooper Flagg</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>REB</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>PHX</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M38" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N38" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
@@ -2765,12 +2764,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -2779,22 +2778,22 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>24.5</v>
+        <v>6.5</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>31.5</v>
+        <v>9.1</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>28.8</v>
+        <v>39.4</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -2808,7 +2807,7 @@
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>0</v>
@@ -2816,7 +2815,7 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
@@ -2825,7 +2824,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2835,17 +2834,17 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>20.5</v>
+        <v>24.5</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>13.1</v>
+        <v>31.5</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-36.3</v>
+        <v>28.8</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
@@ -2868,7 +2867,7 @@
         </is>
       </c>
       <c r="M40" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>0</v>
@@ -2876,7 +2875,7 @@
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
@@ -2885,36 +2884,36 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Caleb Martin</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>11.5</v>
+        <v>20.5</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>16.2</v>
+        <v>13.1</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>40.5</v>
+        <v>-36.3</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
@@ -2928,135 +2927,135 @@
         </is>
       </c>
       <c r="M41" s="4" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Caleb Martin</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N42" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>Reed Sheppard</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>REB</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="F43" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G43" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="H43" s="3" t="n">
         <v>59.3</v>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="I43" s="3" t="inlineStr">
         <is>
           <t>LAC</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M42" s="2" t="n">
+      <c r="M43" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="N42" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Kevin Durant</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>REB</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="N43" s="2" t="n">
+      <c r="N43" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
@@ -3065,12 +3064,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -3079,17 +3078,17 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>16.5</v>
+        <v>4.5</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>23.5</v>
+        <v>5.9</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>42.7</v>
+        <v>31.7</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -3104,264 +3103,264 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr"/>
-      <c r="N44" s="3" t="n"/>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>OG Anunoby</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>Mikal Bridges</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F45" s="2" t="n">
+      <c r="F46" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G46" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="H45" s="2" t="n">
+      <c r="H46" s="3" t="n">
         <v>37.2</v>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>IND</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M45" s="2" t="n">
+      <c r="M46" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="N45" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="N46" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Pascal Siakam</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="F47" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G47" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="H46" s="2" t="n">
+      <c r="H47" s="3" t="n">
         <v>44.5</v>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="I47" s="3" t="inlineStr">
         <is>
           <t>NYK</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M46" s="2" t="n">
+      <c r="M47" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="N46" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="N47" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>Karl-Anthony Towns</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F47" s="2" t="n">
+      <c r="F48" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G48" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="H47" s="2" t="n">
+      <c r="H48" s="3" t="n">
         <v>31.7</v>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr">
         <is>
           <t>IND</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M47" s="2" t="n">
+      <c r="M48" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="N47" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Andrew Nembhard</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>-48</v>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>NYK</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M48" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="N48" s="4" t="n">
-        <v>0</v>
+      <c r="N48" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Alex Caruso</t>
+          <t>Andrew Nembhard</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3375,17 +3374,17 @@
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>6.5</v>
+        <v>16.5</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>3.1</v>
+        <v>8.6</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>-52.3</v>
+        <v>-48</v>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3404,311 +3403,311 @@
         </is>
       </c>
       <c r="M49" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="N49" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="A50" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Draymond Green</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>REB</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Alex Caruso</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="F50" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>-30.4</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>MEM</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N50" s="2" t="n">
-        <v>1</v>
+      <c r="F50" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>-52.3</v>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="N50" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Draymond Green</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>-30.4</v>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Jalen Johnson</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="F51" s="3" t="n">
+      <c r="F52" s="2" t="n">
         <v>8.5</v>
       </c>
-      <c r="G51" s="3" t="n">
+      <c r="G52" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H51" s="3" t="n">
+      <c r="H52" s="2" t="n">
         <v>-48.3</v>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="M51" s="3" t="inlineStr"/>
-      <c r="N51" s="3" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="n">
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>Tyrese Maxey</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="F53" s="4" t="n">
         <v>6.5</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G53" s="4" t="n">
         <v>10.8</v>
       </c>
-      <c r="H52" s="4" t="n">
+      <c r="H53" s="4" t="n">
         <v>66.3</v>
       </c>
-      <c r="I52" s="4" t="inlineStr">
+      <c r="I53" s="4" t="inlineStr">
         <is>
           <t>POR</t>
         </is>
       </c>
-      <c r="J52" s="4" t="inlineStr">
+      <c r="J53" s="4" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="M52" s="4" t="n">
+      <c r="M53" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="N52" s="4" t="n">
+      <c r="N53" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
+    <row r="54">
+      <c r="A54" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>Jaren Jackson Jr.</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>REB</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="F54" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G54" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="H53" s="2" t="n">
+      <c r="H54" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M53" s="2" t="n">
+      <c r="M54" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="N53" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>Lauri Markkanen</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G54" s="4" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="H54" s="4" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="I54" s="4" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K54" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M54" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="N54" s="4" t="n">
-        <v>0</v>
+      <c r="N54" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
@@ -3717,12 +3716,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Lauri Markkanen</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -3731,22 +3730,22 @@
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>3.5</v>
+        <v>22.5</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>6</v>
+        <v>28.6</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>72.2</v>
+        <v>27.2</v>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -3760,315 +3759,315 @@
         </is>
       </c>
       <c r="M55" s="4" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="N55" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Desmond Bane</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>Paolo Banchero</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>REB</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="F57" s="3" t="n">
         <v>9.5</v>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G57" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="H56" s="2" t="n">
+      <c r="H57" s="3" t="n">
         <v>-34.6</v>
       </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J57" s="3" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M56" s="2" t="n">
+      <c r="M57" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="N56" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="N57" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>LaMelo Ball</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>REB</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F57" s="2" t="n">
+      <c r="F58" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G58" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="H57" s="2" t="n">
+      <c r="H58" s="3" t="n">
         <v>111.4</v>
       </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="I58" s="3" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="J58" s="3" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M57" s="2" t="n">
+      <c r="M58" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="N57" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="n">
+      <c r="N58" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>Brandon Miller</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>REB</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="F59" s="4" t="n">
         <v>4.5</v>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G59" s="4" t="n">
         <v>5.8</v>
       </c>
-      <c r="H58" s="4" t="n">
+      <c r="H59" s="4" t="n">
         <v>28.1</v>
       </c>
-      <c r="I58" s="4" t="inlineStr">
+      <c r="I59" s="4" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="J58" s="4" t="inlineStr">
+      <c r="J59" s="4" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K58" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="M58" s="4" t="n">
+      <c r="M59" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N58" s="4" t="n">
+      <c r="N59" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
+    <row r="60">
+      <c r="A60" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>Julius Randle</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="F59" s="2" t="n">
+      <c r="F60" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G60" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="H59" s="2" t="n">
+      <c r="H60" s="3" t="n">
         <v>-41.8</v>
       </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr">
         <is>
           <t>LAC</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M59" s="2" t="n">
+      <c r="M60" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N59" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>Anthony Edwards</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G60" s="4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H60" s="4" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K60" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M60" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N60" s="4" t="n">
-        <v>0</v>
+      <c r="N60" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
@@ -4077,7 +4076,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -4094,19 +4093,19 @@
         <v>3.5</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>47.1</v>
+        <v>53.3</v>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -4128,7 +4127,7 @@
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
@@ -4137,7 +4136,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Pascal Siakam</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -4154,19 +4153,19 @@
         <v>3.5</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>34</v>
+        <v>47.1</v>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -4180,369 +4179,429 @@
         </is>
       </c>
       <c r="M62" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N62" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Brandon Ingram</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M63" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N63" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>Andrew Nembhard</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="F63" s="2" t="n">
+      <c r="F64" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G64" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="H63" s="2" t="n">
+      <c r="H64" s="3" t="n">
         <v>-44.7</v>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="J64" s="3" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M63" s="2" t="n">
+      <c r="M64" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N63" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="N64" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="F64" s="2" t="n">
+      <c r="F65" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="G65" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="H64" s="2" t="n">
+      <c r="H65" s="3" t="n">
         <v>-47</v>
       </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="I65" s="3" t="inlineStr">
         <is>
           <t>WAS</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="J65" s="3" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M64" s="2" t="n">
+      <c r="M65" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="N64" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="N65" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>Norman Powell</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="F66" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="G65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H65" s="2" t="n">
+      <c r="G66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="3" t="n">
         <v>-60.8</v>
       </c>
-      <c r="I65" s="2" t="inlineStr">
+      <c r="I66" s="3" t="inlineStr">
         <is>
           <t>WAS</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M65" s="2" t="n">
+      <c r="M66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N65" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="N66" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>Andrew Wiggins</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="F66" s="2" t="n">
+      <c r="F67" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="G67" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="H66" s="2" t="n">
+      <c r="H67" s="3" t="n">
         <v>-40.4</v>
       </c>
-      <c r="I66" s="2" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr">
         <is>
           <t>WAS</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M66" s="2" t="n">
+      <c r="M67" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N66" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="N67" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>Bam Adebayo</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F67" s="2" t="n">
+      <c r="F68" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="G68" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="H67" s="2" t="n">
+      <c r="H68" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="I67" s="2" t="inlineStr">
+      <c r="I68" s="3" t="inlineStr">
         <is>
           <t>WAS</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="J68" s="3" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M67" s="2" t="n">
+      <c r="M68" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="N67" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="N68" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>Jaylen Brown</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>REB</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="F68" s="2" t="n">
+      <c r="F69" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="G69" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="H68" s="2" t="n">
+      <c r="H69" s="3" t="n">
         <v>-47.6</v>
       </c>
-      <c r="I68" s="2" t="inlineStr">
+      <c r="I69" s="3" t="inlineStr">
         <is>
           <t>NYK</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="J69" s="3" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M68" s="2" t="n">
+      <c r="M69" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N68" s="2" t="n">
+      <c r="N69" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4557,18 +4616,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4615,6 +4674,47 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>OG Anunoby</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
         </is>
       </c>
     </row>
@@ -4640,24 +4740,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>OVERALL PERFORMANCE</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Total Picks</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Graded Picks</t>
         </is>
@@ -4667,7 +4767,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
@@ -4677,7 +4777,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Losses</t>
         </is>
@@ -4687,7 +4787,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
@@ -4699,7 +4799,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>ROI</t>
         </is>
@@ -4711,7 +4811,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Avg Edge (Winners)</t>
         </is>
@@ -4723,217 +4823,217 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-02-13 09:27</t>
+          <t>2026-02-17 15:03</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>PERFORMANCE BY MODEL</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Losses</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>ROI</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C16" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>56.1%</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>+7.2%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>PERFORMANCE BY STAT</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n">
+      <c r="B22" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="C22" s="8" t="n">
+      <c r="C22" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>REB</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n">
+      <c r="B23" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C23" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="B24" s="8" t="n">
+      <c r="B24" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="C24" s="8" t="n">
+      <c r="C24" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>62.5%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>PRA</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n">
+      <c r="B25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>PERFORMANCE BY EDGE RANGE</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Edge Range</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>12%+</t>
         </is>
       </c>
-      <c r="B31" s="8" t="n">
+      <c r="B31" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="C31" s="8" t="n">
+      <c r="C31" s="9" t="n">
         <v>54</v>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>55.6%</t>
         </is>
@@ -4963,760 +5063,760 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Profit/Loss</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Cumulative Profit</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="8" t="n">
+      <c r="B2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="8" t="n">
+      <c r="B3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="8" t="n">
+      <c r="B4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="8" t="n">
+      <c r="B5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="9" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="8" t="n">
+      <c r="B6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="9" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="8" t="n">
+      <c r="B7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="9" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="9" t="n">
         <v>4.9</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="9" t="n">
         <v>3.8</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C10" s="9" t="n">
         <v>2.7</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="8" t="n">
+      <c r="B11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="9" t="n">
         <v>3.7</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="9" t="n">
         <v>2.6</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="8" t="n">
+      <c r="B13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="9" t="n">
         <v>3.6</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="8" t="n">
+      <c r="B14" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="9" t="n">
         <v>4.6</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B15" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="9" t="n">
         <v>3.5</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
+      <c r="B16" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C16" s="9" t="n">
         <v>2.4</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="8" t="n">
+      <c r="B17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="9" t="n">
         <v>3.4</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
+      <c r="B18" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C18" s="9" t="n">
         <v>2.3</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="8" t="n">
+      <c r="B19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="9" t="n">
         <v>3.3</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n">
+      <c r="B20" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C20" s="9" t="n">
         <v>2.2</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
+      <c r="B21" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="9" t="n">
         <v>1.1</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="8" t="n">
+      <c r="B22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="9" t="n">
         <v>2.1</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="8" t="n">
+      <c r="B23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="9" t="n">
         <v>3.1</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="8" t="n">
+      <c r="B24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="9" t="n">
         <v>4.1</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="8" t="n">
+      <c r="B25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="9" t="n">
         <v>5.1</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="8" t="n">
+      <c r="B26" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="9" t="n">
         <v>6.1</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n">
+      <c r="B27" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C27" s="8" t="n">
+      <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n">
+      <c r="B28" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C28" s="8" t="n">
+      <c r="C28" s="9" t="n">
         <v>3.9</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n">
+      <c r="B29" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C29" s="8" t="n">
+      <c r="C29" s="9" t="n">
         <v>2.8</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n">
+      <c r="B30" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C30" s="8" t="n">
+      <c r="C30" s="9" t="n">
         <v>1.7</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n">
+      <c r="B31" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C31" s="8" t="n">
+      <c r="C31" s="9" t="n">
         <v>0.6</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n">
+      <c r="B32" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C32" s="8" t="n">
+      <c r="C32" s="9" t="n">
         <v>-0.5</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="8" t="n">
+      <c r="B33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="9" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B34" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="8" t="n">
+      <c r="B34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="9" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="8" t="n">
+      <c r="B35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="9" t="n">
         <v>2.5</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B36" s="10" t="n">
+      <c r="B36" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C36" s="8" t="n">
+      <c r="C36" s="9" t="n">
         <v>1.4</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="8" t="n">
+      <c r="B37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="9" t="n">
         <v>2.4</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B38" s="10" t="n">
+      <c r="B38" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C38" s="8" t="n">
+      <c r="C38" s="9" t="n">
         <v>1.3</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B39" s="10" t="n">
+      <c r="B39" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C39" s="8" t="n">
+      <c r="C39" s="9" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B40" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="8" t="n">
+      <c r="B40" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="9" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B41" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="8" t="n">
+      <c r="B41" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="9" t="n">
         <v>2.2</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B42" s="10" t="n">
+      <c r="B42" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C42" s="8" t="n">
+      <c r="C42" s="9" t="n">
         <v>1.1</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B43" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" s="8" t="n">
+      <c r="B43" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="9" t="n">
         <v>2.1</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" s="8" t="n">
+      <c r="B44" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="9" t="n">
         <v>3.1</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B45" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="8" t="n">
+      <c r="B45" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="9" t="n">
         <v>4.1</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B46" s="10" t="n">
+      <c r="B46" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C46" s="8" t="n">
+      <c r="C46" s="9" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B47" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" s="8" t="n">
+      <c r="B47" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="9" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B48" s="10" t="n">
+      <c r="B48" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C48" s="8" t="n">
+      <c r="C48" s="9" t="n">
         <v>2.9</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B49" s="10" t="n">
+      <c r="B49" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C49" s="8" t="n">
+      <c r="C49" s="9" t="n">
         <v>1.8</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B50" s="10" t="n">
+      <c r="B50" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C50" s="8" t="n">
+      <c r="C50" s="9" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B51" s="10" t="n">
+      <c r="B51" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C51" s="8" t="n">
+      <c r="C51" s="9" t="n">
         <v>-0.4</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B52" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" s="8" t="n">
+      <c r="B52" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="9" t="n">
         <v>0.6</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B53" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" s="8" t="n">
+      <c r="B53" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="9" t="n">
         <v>1.6</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="B54" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" s="8" t="n">
+      <c r="B54" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="9" t="n">
         <v>2.6</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="B55" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" s="8" t="n">
+      <c r="B55" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="9" t="n">
         <v>3.6</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="B56" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" s="8" t="n">
+      <c r="B56" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="9" t="n">
         <v>4.6</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="B57" s="10" t="n">
+      <c r="B57" s="11" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C57" s="8" t="n">
+      <c r="C57" s="9" t="n">
         <v>3.5</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="B58" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" s="8" t="n">
+      <c r="B58" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="9" t="n">
         <v>4.5</v>
       </c>
     </row>

--- a/nba_picks_tracker.xlsx
+++ b/nba_picks_tracker.xlsx
@@ -40,7 +40,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +71,18 @@
         <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0090EE90"/>
+        <bgColor rgb="0090EE90"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -90,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -104,7 +116,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -478,12 +493,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
@@ -571,7 +586,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -580,7 +595,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -590,26 +605,26 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>19.7</v>
+        <v>8</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>4.2</v>
+        <v>-40.7</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -627,7 +642,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -636,31 +651,31 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>15.5</v>
+        <v>3.5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>19.8</v>
+        <v>2.3</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>27.5</v>
+        <v>-34.3</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -683,7 +698,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -692,36 +707,36 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Grant Williams</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>-0.9</v>
+        <v>60</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -739,7 +754,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
@@ -748,12 +763,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -762,22 +777,22 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>19.5</v>
+        <v>6</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>4</v>
+        <v>33.3</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -795,16 +810,16 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -818,17 +833,17 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>99.3</v>
+        <v>77.8</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -850,978 +865,926 @@
       <c r="N6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Justin Champagnie</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>-65.7</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Andrew Nembhard</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>-41.2</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Pascal Siakam</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Nolan Traore</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>-31.1</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Quentin Grimes</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>-31.4</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>VJ Edgecombe</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Dyson Daniels</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Kelly Oubre Jr.</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Jalen Johnson</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>-23.5</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>OG Anunoby</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Austin Reaves</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G21" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H21" s="3" t="n">
         <v>-35.2</v>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>DAL</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M21" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N21" s="3" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
+    <row r="22">
+      <c r="A22" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Cam Thomas</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>PRA</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F22" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>29.7</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>31.9</v>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>OKC</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="M22" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="N22" s="4" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Aaron Wiggins</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-37.7</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Chet Holmgren</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Kevin Porter Jr.</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>-78.3</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>OKC</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>De'Aaron Fox</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>GSW</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Victor Wembanyama</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>148.8</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>GSW</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Dillon Brooks</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>-33.7</v>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>OKC</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Reed Sheppard</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>REB</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N15" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Anthony Edwards</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N16" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Jaime Jaquez Jr.</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>-49.6</v>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>NOP</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="N17" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Trey Murphy III</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>-33</v>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Tyrese Maxey</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>REB</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>NYK</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Kelly Oubre Jr.</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>REB</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>NYK</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>OG Anunoby</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Karl-Anthony Towns</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Collin Sexton</t>
+          <t>Aaron Wiggins</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1830,22 +1793,22 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>4.5</v>
+        <v>16.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2.6</v>
+        <v>10.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-41.9</v>
+        <v>-37.7</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -1859,131 +1822,135 @@
         </is>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Andrew Nembhard</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="A24" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Chet Holmgren</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Kevin Porter Jr.</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>-50.1</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>BKN</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="F25" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>-78.3</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Brandon Ingram</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="4" t="n">
-        <v>0</v>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -1992,12 +1959,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2006,17 +1973,17 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>2.5</v>
+        <v>18.5</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>3.1</v>
+        <v>24.5</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>24.9</v>
+        <v>32.4</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -2035,7 +2002,7 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>1</v>
@@ -2043,7 +2010,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -2052,12 +2019,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -2066,17 +2033,17 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>14.8</v>
+        <v>6.2</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>40.7</v>
+        <v>148.8</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2095,7 +2062,7 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1</v>
@@ -2103,7 +2070,7 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
@@ -2112,31 +2079,31 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.5</v>
+        <v>19.5</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>7.9</v>
+        <v>12.9</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>44.4</v>
+        <v>-33.7</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2155,7 +2122,7 @@
         </is>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0</v>
@@ -2163,7 +2130,7 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
@@ -2172,36 +2139,36 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-50.1</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -2215,75 +2182,75 @@
         </is>
       </c>
       <c r="M29" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="A30" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Paolo Banchero</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>REB</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>-39.7</v>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Anthony Edwards</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>1</v>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
@@ -2292,36 +2259,36 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>44.2</v>
+        <v>-49.6</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -2335,7 +2302,7 @@
         </is>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>0</v>
@@ -2343,7 +2310,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -2352,36 +2319,36 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>1.5</v>
+        <v>22.5</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>2.5</v>
+        <v>15.1</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>-33</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -2395,113 +2362,113 @@
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="A33" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Desmond Bane</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="F33" s="4" t="n">
         <v>3.5</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="G33" s="4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>1</v>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N33" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>-35.4</v>
+        <v>40.9</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -2515,7 +2482,7 @@
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>1</v>
@@ -2523,21 +2490,21 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>OG Anunoby</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2546,22 +2513,22 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>5.5</v>
+        <v>15.5</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>31.6</v>
+        <v>35.2</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2578,137 +2545,137 @@
       <c r="N35" s="2" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>De'Aaron Fox</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="A36" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Karl-Anthony Towns</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F36" s="4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>LAL</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="F36" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="N36" s="4" t="n">
-        <v>0</v>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Victor Wembanyama</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="A37" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Collin Sexton</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>138.8</v>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>LAL</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>-41.9</v>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N37" s="4" t="n">
-        <v>0</v>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Klay Thompson</t>
+          <t>Andrew Nembhard</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2718,21 +2685,21 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>8.5</v>
+        <v>18.5</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>29.9</v>
+        <v>-50.1</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2755,21 +2722,21 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Cooper Flagg</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -2778,22 +2745,22 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>9.1</v>
+        <v>4.7</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>39.4</v>
+        <v>35.7</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -2807,149 +2774,149 @@
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Devin Booker</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="A40" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Dyson Daniels</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F40" s="4" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="N40" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Dillon Brooks</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>-36.3</v>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="N41" s="4" t="n">
-        <v>0</v>
+      <c r="F41" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Caleb Martin</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -2958,22 +2925,22 @@
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>16.2</v>
+        <v>7.9</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>40.5</v>
+        <v>44.4</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
@@ -2987,84 +2954,84 @@
         </is>
       </c>
       <c r="M42" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N42" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Reed Sheppard</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>REB</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v>1</v>
+      <c r="A43" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Jalen Johnson</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>-50.1</v>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N43" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -3074,21 +3041,21 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>31.7</v>
+        <v>-39.7</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -3107,85 +3074,89 @@
         </is>
       </c>
       <c r="M44" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>OG Anunoby</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="A45" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Jalen Suggs</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F45" s="2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>IND</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="F45" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="n"/>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Myles Turner</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -3194,22 +3165,22 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>14.5</v>
+        <v>1.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>19.9</v>
+        <v>2.5</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>37.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
@@ -3223,7 +3194,7 @@
         </is>
       </c>
       <c r="M46" s="3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>1</v>
@@ -3231,16 +3202,16 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -3257,19 +3228,19 @@
         <v>3.5</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>44.5</v>
+        <v>72.3</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
@@ -3283,7 +3254,7 @@
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N47" s="3" t="n">
         <v>1</v>
@@ -3291,7 +3262,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
@@ -3300,36 +3271,36 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>31.7</v>
+        <v>-35.4</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
@@ -3343,84 +3314,80 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="A49" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Andrew Nembhard</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H49" s="4" t="n">
-        <v>-48</v>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>NYK</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M49" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="N49" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>LeBron James</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Alex Caruso</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3430,17 +3397,17 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>6.5</v>
+        <v>17.5</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>3.1</v>
+        <v>24.9</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>-52.3</v>
+        <v>42.4</v>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
@@ -3463,108 +3430,108 @@
         </is>
       </c>
       <c r="M50" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="N50" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>Draymond Green</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>REB</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H51" s="3" t="n">
-        <v>-30.4</v>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>MEM</t>
-        </is>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="N51" s="3" t="n">
-        <v>1</v>
+      <c r="A51" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Victor Wembanyama</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>138.8</v>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N51" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Klay Thompson</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
         <v>8.5</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>-48.3</v>
+        <v>29.9</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3587,21 +3554,21 @@
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -3613,14 +3580,14 @@
         <v>6.5</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>10.8</v>
+        <v>9.1</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>66.3</v>
+        <v>39.4</v>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3639,84 +3606,84 @@
         </is>
       </c>
       <c r="M53" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N53" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>Jaren Jackson Jr.</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>REB</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="A54" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Devin Booker</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H54" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M54" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N54" s="3" t="n">
-        <v>1</v>
+      <c r="F54" s="4" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Lauri Markkanen</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -3726,26 +3693,26 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>28.6</v>
+        <v>13.1</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>27.2</v>
+        <v>-36.3</v>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -3759,7 +3726,7 @@
         </is>
       </c>
       <c r="M55" s="4" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="N55" s="4" t="n">
         <v>0</v>
@@ -3767,21 +3734,21 @@
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Caleb Martin</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -3790,22 +3757,22 @@
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>6</v>
+        <v>16.2</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>72.2</v>
+        <v>40.5</v>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
@@ -3819,7 +3786,7 @@
         </is>
       </c>
       <c r="M56" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N56" s="4" t="n">
         <v>0</v>
@@ -3827,16 +3794,16 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -3846,21 +3813,21 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>-34.6</v>
+        <v>59.3</v>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -3879,7 +3846,7 @@
         </is>
       </c>
       <c r="M57" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N57" s="3" t="n">
         <v>1</v>
@@ -3887,16 +3854,16 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -3910,17 +3877,17 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>111.4</v>
+        <v>31.7</v>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -3939,108 +3906,104 @@
         </is>
       </c>
       <c r="M58" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N58" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>Brandon Miller</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>REB</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="A59" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>OG Anunoby</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F59" s="4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G59" s="4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H59" s="4" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
+      <c r="F59" s="2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M59" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N59" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>2.6</v>
+        <v>19.9</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>-41.8</v>
+        <v>37.2</v>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -4059,173 +4022,173 @@
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="N60" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>Anthony Edwards</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="A61" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Pascal Siakam</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="F61" s="4" t="n">
+      <c r="F61" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="G61" s="4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H61" s="4" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="I61" s="4" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
+      <c r="G61" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Karl-Anthony Towns</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K61" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M61" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N61" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>Pascal Siakam</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G62" s="4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="H62" s="4" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K62" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="M62" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N62" s="4" t="n">
-        <v>0</v>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Andrew Nembhard</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>3.5</v>
+        <v>16.5</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>34</v>
+        <v>-48</v>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
@@ -4239,89 +4202,89 @@
         </is>
       </c>
       <c r="M63" s="4" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>Andrew Nembhard</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="A64" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Alex Caruso</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="F64" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>-44.7</v>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
+      <c r="F64" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>-52.3</v>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M64" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N64" s="3" t="n">
-        <v>1</v>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M64" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="N64" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Jaime Jaquez Jr.</t>
+          <t>Draymond Green</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -4330,22 +4293,22 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>14.5</v>
+        <v>5.5</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>-47</v>
+        <v>-30.4</v>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
@@ -4366,142 +4329,138 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>Norman Powell</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="A66" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Jalen Johnson</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="F66" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66" s="3" t="n">
-        <v>-60.8</v>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
+      <c r="F66" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>-48.3</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L66" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M66" s="3" t="n">
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M67" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N67" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="N66" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Andrew Wiggins</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H67" s="3" t="n">
-        <v>-40.4</v>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>AWAY</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="M67" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N67" s="3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Jaren Jackson Jr.</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -4510,17 +4469,17 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>25.2</v>
+        <v>40</v>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -4539,69 +4498,909 @@
         </is>
       </c>
       <c r="M68" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N68" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Lauri Markkanen</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M69" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="N69" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Desmond Bane</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M70" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="N70" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Paolo Banchero</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>-34.6</v>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>LaMelo Ball</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Brandon Miller</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M73" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N73" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Julius Randle</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>-41.8</v>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Anthony Edwards</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M75" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N75" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Pascal Siakam</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M76" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N76" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Brandon Ingram</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M77" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N77" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Andrew Nembhard</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>-44.7</v>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Jaime Jaquez Jr.</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>-47</v>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Norman Powell</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>-60.8</v>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Andrew Wiggins</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>-40.4</v>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Bam Adebayo</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>Jaylen Brown</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>REB</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="F69" s="3" t="n">
+      <c r="F83" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="G69" s="3" t="n">
+      <c r="G83" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="H69" s="3" t="n">
+      <c r="H83" s="3" t="n">
         <v>-47.6</v>
       </c>
-      <c r="I69" s="3" t="inlineStr">
+      <c r="I83" s="3" t="inlineStr">
         <is>
           <t>NYK</t>
         </is>
       </c>
-      <c r="J69" s="3" t="inlineStr">
+      <c r="J83" s="3" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="M69" s="3" t="n">
+      <c r="M83" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N69" s="3" t="n">
+      <c r="N83" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4616,10 +5415,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -4680,39 +5479,777 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>LaMelo Ball</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Justin Champagnie</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-65.7</v>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Grant Williams</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Nolan Traore</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-56</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Pascal Siakam</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Andrew Nembhard</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-41.2</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Dyson Daniels</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Tari Eason</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-40.7</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Brandon Miller</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-34.3</v>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Kevin Durant</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Quentin Grimes</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-31.4</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-31.1</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
           <t>OG Anunoby</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D17" s="6" t="n">
         <v>15.5</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E17" s="6" t="n">
         <v>19.7</v>
       </c>
-      <c r="F2" s="5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="F17" s="6" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Kelly Oubre Jr.</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Jalen Johnson</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-23.5</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>VJ Edgecombe</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>Gradient Boost</t>
         </is>
@@ -4740,24 +6277,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>OVERALL PERFORMANCE</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Total Picks</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Graded Picks</t>
         </is>
@@ -4767,7 +6304,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
@@ -4777,7 +6314,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Losses</t>
         </is>
@@ -4787,7 +6324,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
@@ -4799,7 +6336,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>ROI</t>
         </is>
@@ -4811,7 +6348,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Avg Edge (Winners)</t>
         </is>
@@ -4823,217 +6360,217 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-02-17 15:03</t>
+          <t>2026-02-17 16:20</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>PERFORMANCE BY MODEL</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Losses</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>ROI</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="n">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>56.1%</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>+7.2%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>PERFORMANCE BY STAT</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>REB</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n">
+      <c r="B23" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>60.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B24" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>62.5%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>PRA</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n">
+      <c r="B25" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>PERFORMANCE BY EDGE RANGE</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Edge Range</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>12%+</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n">
+      <c r="B31" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>55.6%</t>
         </is>
@@ -5063,760 +6600,760 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Profit/Loss</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Cumulative Profit</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n">
+      <c r="B2" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C2" s="10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C3" s="10" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" s="10" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="10" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="10" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="10" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="10" t="n">
         <v>4.9</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="10" t="n">
         <v>3.8</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>2.7</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="10" t="n">
         <v>3.7</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="10" t="n">
         <v>2.6</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="10" t="n">
         <v>3.6</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n">
+      <c r="B14" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="10" t="n">
         <v>4.6</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="10" t="n">
         <v>3.5</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="10" t="n">
         <v>2.4</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B17" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="10" t="n">
         <v>3.4</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B18" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="10" t="n">
         <v>2.3</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
+      <c r="B19" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="10" t="n">
         <v>3.3</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n">
+      <c r="B20" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="10" t="n">
         <v>2.2</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B21" s="11" t="n">
+      <c r="B21" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" s="10" t="n">
         <v>1.1</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
+      <c r="B22" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="10" t="n">
         <v>2.1</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
+      <c r="B23" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="10" t="n">
         <v>3.1</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B24" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="10" t="n">
         <v>4.1</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
+      <c r="B25" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="10" t="n">
         <v>5.1</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
+      <c r="B26" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C26" s="10" t="n">
         <v>6.1</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n">
+      <c r="B27" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" s="10" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n">
+      <c r="B28" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" s="10" t="n">
         <v>3.9</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n">
+      <c r="B29" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C29" s="10" t="n">
         <v>2.8</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B30" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C30" s="9" t="n">
+      <c r="C30" s="10" t="n">
         <v>1.7</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B31" s="11" t="n">
+      <c r="B31" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="10" t="n">
         <v>0.6</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n">
+      <c r="B32" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C32" s="9" t="n">
+      <c r="C32" s="10" t="n">
         <v>-0.5</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B33" s="10" t="n">
+      <c r="B33" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C33" s="9" t="n">
+      <c r="C33" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B34" s="10" t="n">
+      <c r="B34" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="9" t="n">
+      <c r="C34" s="10" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n">
+      <c r="B35" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="9" t="n">
+      <c r="C35" s="10" t="n">
         <v>2.5</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B36" s="11" t="n">
+      <c r="B36" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C36" s="9" t="n">
+      <c r="C36" s="10" t="n">
         <v>1.4</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B37" s="10" t="n">
+      <c r="B37" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="9" t="n">
+      <c r="C37" s="10" t="n">
         <v>2.4</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B38" s="11" t="n">
+      <c r="B38" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C38" s="9" t="n">
+      <c r="C38" s="10" t="n">
         <v>1.3</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B39" s="11" t="n">
+      <c r="B39" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C39" s="9" t="n">
+      <c r="C39" s="10" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B40" s="10" t="n">
+      <c r="B40" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="9" t="n">
+      <c r="C40" s="10" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B41" s="10" t="n">
+      <c r="B41" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C41" s="9" t="n">
+      <c r="C41" s="10" t="n">
         <v>2.2</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n">
+      <c r="B42" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C42" s="9" t="n">
+      <c r="C42" s="10" t="n">
         <v>1.1</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B43" s="10" t="n">
+      <c r="B43" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="9" t="n">
+      <c r="C43" s="10" t="n">
         <v>2.1</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B44" s="10" t="n">
+      <c r="B44" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C44" s="9" t="n">
+      <c r="C44" s="10" t="n">
         <v>3.1</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B45" s="10" t="n">
+      <c r="B45" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="9" t="n">
+      <c r="C45" s="10" t="n">
         <v>4.1</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B46" s="11" t="n">
+      <c r="B46" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C46" s="9" t="n">
+      <c r="C46" s="10" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B47" s="10" t="n">
+      <c r="B47" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="9" t="n">
+      <c r="C47" s="10" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B48" s="11" t="n">
+      <c r="B48" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C48" s="9" t="n">
+      <c r="C48" s="10" t="n">
         <v>2.9</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B49" s="11" t="n">
+      <c r="B49" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C49" s="9" t="n">
+      <c r="C49" s="10" t="n">
         <v>1.8</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B50" s="11" t="n">
+      <c r="B50" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C50" s="9" t="n">
+      <c r="C50" s="10" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B51" s="11" t="n">
+      <c r="B51" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C51" s="9" t="n">
+      <c r="C51" s="10" t="n">
         <v>-0.4</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B52" s="10" t="n">
+      <c r="B52" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="9" t="n">
+      <c r="C52" s="10" t="n">
         <v>0.6</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="B53" s="10" t="n">
+      <c r="B53" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="9" t="n">
+      <c r="C53" s="10" t="n">
         <v>1.6</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="B54" s="10" t="n">
+      <c r="B54" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="9" t="n">
+      <c r="C54" s="10" t="n">
         <v>2.6</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="B55" s="10" t="n">
+      <c r="B55" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="9" t="n">
+      <c r="C55" s="10" t="n">
         <v>3.6</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="B56" s="10" t="n">
+      <c r="B56" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="9" t="n">
+      <c r="C56" s="10" t="n">
         <v>4.6</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="B57" s="11" t="n">
+      <c r="B57" s="12" t="n">
         <v>-1.1</v>
       </c>
-      <c r="C57" s="9" t="n">
+      <c r="C57" s="10" t="n">
         <v>3.5</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="B58" s="10" t="n">
+      <c r="B58" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C58" s="9" t="n">
+      <c r="C58" s="10" t="n">
         <v>4.5</v>
       </c>
     </row>

--- a/nba_picks_tracker.xlsx
+++ b/nba_picks_tracker.xlsx
@@ -40,7 +40,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
         <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -90,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -104,12 +116,21 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -475,12 +496,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
@@ -568,16 +589,16 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -591,22 +612,22 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>27.5</v>
+        <v>39.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>31.9</v>
+        <v>44.5</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>16</v>
+        <v>12.7</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -624,16 +645,16 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Bennedict Mathurin</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -647,22 +668,22 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>20</v>
+        <v>32.7</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -680,45 +701,45 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Nic Claxton</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>44.4</v>
+        <v>-22.7</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -736,16 +757,16 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Alperen Sengun</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -759,22 +780,22 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>41.5</v>
+        <v>28</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -792,21 +813,21 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Ben Sheppard</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -815,22 +836,22 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>15.5</v>
+        <v>8.5</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>19.4</v>
+        <v>12.5</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>25.2</v>
+        <v>47.1</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -848,21 +869,21 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Norman Powell</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -871,17 +892,17 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>-20</v>
+        <v>-84</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -904,16 +925,16 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Kevin Porter Jr.</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -927,17 +948,17 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>37.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -960,21 +981,21 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -983,17 +1004,17 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>11.2</v>
+        <v>19.9</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>17.9</v>
+        <v>37.2</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1016,16 +1037,16 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Immanuel Quickley</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1035,26 +1056,26 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G10" s="2" t="n">
         <v>5.5</v>
       </c>
-      <c r="G10" s="2" t="n">
-        <v>4.5</v>
-      </c>
       <c r="H10" s="2" t="n">
-        <v>-18.2</v>
+        <v>57.1</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1072,21 +1093,21 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1095,22 +1116,22 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>6.5</v>
+        <v>27.5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>11.2</v>
+        <v>35.4</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>72.3</v>
+        <v>28.7</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1128,21 +1149,21 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1151,17 +1172,17 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>22.6</v>
+        <v>6.9</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>80.8</v>
+        <v>25.5</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1184,21 +1205,21 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1207,17 +1228,17 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>13.2</v>
+        <v>18.8</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>14.8</v>
+        <v>29.7</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1239,120 +1260,128 @@
       <c r="N13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>168</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>2026-02-24</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Brandon Ingram</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Derrick White</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>179</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Derrick White</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>SAS</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>167</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Julian Champagnie</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="G15" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="n"/>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
@@ -1361,12 +1390,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1378,19 +1407,19 @@
         <v>4.5</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>51.1</v>
+        <v>44.4</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1407,60 +1436,664 @@
       <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>165</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="n">
+        <v>177</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>2026-02-24</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Isaiah Joe</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Alperen Sengun</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Malik Monk</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Kevin Porter Jr.</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>173</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>172</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Immanuel Quickley</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>-18.2</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>171</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Stephon Castle</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Devin Vassell</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>AWAY</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="n"/>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>169</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Victor Wembanyama</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Brandon Ingram</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Julian Champagnie</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>AWAY</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>166</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1473,10 +2106,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -1535,656 +2168,533 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Devin Vassell</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Norman Powell</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>-84</v>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Tyler Herro</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Ben Sheppard</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E5" s="5" t="n">
         <v>12.5</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="F5" s="5" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Jaylen Brown</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Stephon Castle</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Tyler Herro</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Bennedict Mathurin</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Andrew Wiggins</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Joel Embiid</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Victor Wembanyama</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tobias Harris</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Andrew Wiggins</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>REB</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>OKC</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Julian Champagnie</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Jaylen Brown</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Alperen Sengun</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>SAC</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Kevin Porter Jr.</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Nic Claxton</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>REB</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Brandon Ingram</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-22.7</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>SAS</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Isaiah Joe</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Malik Monk</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Kawhi Leonard</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>PRA</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Derrick White</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>REB</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Donovan Mitchell</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>REB</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>-20</v>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Immanuel Quickley</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>-18.2</v>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>SAS</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Jarrett Allen</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>REB</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Derrick White</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>PRA</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>Gradient Boost</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Victor Wembanyama</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>REB</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Gradient Boost</t>
         </is>
@@ -2201,7 +2711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2212,189 +2722,302 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>OVERALL PERFORMANCE</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Total Picks</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Graded Picks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Losses</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>ROI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+46.9%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Avg Edge (Winners)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>36.6%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-02-24 23:38</t>
+          <t>2026-02-25 23:00</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>PERFORMANCE BY MODEL</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Losses</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>ROI</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Gradient Boost</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>76.9%</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>+46.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>PERFORMANCE BY STAT</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>PERFORMANCE BY EDGE RANGE</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Edge Range</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Wins</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>Win Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>12%+</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -2413,7 +3036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2422,20 +3045,189 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Profit/Loss</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Cumulative Profit</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
